--- a/data/grondwater_template_full.xlsx
+++ b/data/grondwater_template_full.xlsx
@@ -8812,7 +8812,7 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2024-07-24 09:00:00.093005</t>
+    <t>2024-07-24 09:03:31.254233</t>
   </si>
   <si>
     <t>version</t>
